--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED23.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED23.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>189W</t>
+          <t>183W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0165</t>
+          <t>SIM_XA_FIXED-2-0013</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30W</t>
+          <t>51W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3季</t>
+          <t>2季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,14 +1748,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-3-0141</t>
+          <t>SIM_XA_FIXED-4-0164</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1769,11 +1769,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>39W</t>
+          <t>134W</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>第3年</t>
+          <t>第4年</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1季</t>
+          <t>4季</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
     </row>
@@ -2189,14 +2189,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auction_Win</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-10</v>
+        <v>-24</v>
       </c>
       <c r="E16" t="n">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="E17" t="n">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-0cd5ac2444", "line_id": "L-574738229a", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2241,23 +2241,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年2季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2267,14 +2267,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E19" t="n">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-aada62c91b", "line_id": "L-574738229a", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2293,23 +2293,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-2-0013", "receivable_term_quarters": 2, "revenue_wan": 51.0}</t>
         </is>
       </c>
     </row>
@@ -2319,14 +2319,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="E21" t="n">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="E22" t="n">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-574738229a"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-6a30382f99", "line_id": "L-574738229a", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>383</v>
+        <v>348</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-574738229a", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2397,14 +2397,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E24" t="n">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-574738229a", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-574738229a"}</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2423,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0165", "receivable_term_quarters": 3, "revenue_wan": 30.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-574738229a", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2449,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>371</v>
+        <v>333</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-574738229a", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2475,14 +2475,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>-8</v>
       </c>
       <c r="E27" t="n">
-        <v>363</v>
+        <v>325</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-5efd7dafb5", "line_id": "L-574738229a", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2501,14 +2501,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E28" t="n">
-        <v>355</v>
+        <v>311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2527,14 +2527,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-14</v>
+        <v>51</v>
       </c>
       <c r="E29" t="n">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-1d3546a731"}</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
         <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2605,23 +2605,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>30</v>
+        <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>343</v>
+        <v>320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-ddedd1870d"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2631,14 +2631,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E33" t="n">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0141", "receivable_term_quarters": 1, "revenue_wan": 39.0}</t>
+          <t>maintenance_expense | {"line_id": "L-574738229a"}</t>
         </is>
       </c>
     </row>
@@ -2657,14 +2657,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-574738229a", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2683,14 +2683,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-07303b20dc", "line_id": "L-574738229a", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-574738229a", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2709,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E36" t="n">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2735,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>-14</v>
       </c>
       <c r="E37" t="n">
-        <v>348</v>
+        <v>283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-678226538f"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2761,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-15</v>
+        <v>-24</v>
       </c>
       <c r="E38" t="n">
-        <v>333</v>
+        <v>259</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-574738229a"}</t>
+          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
         </is>
       </c>
     </row>
@@ -2787,23 +2787,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="E39" t="n">
-        <v>333</v>
+        <v>243</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-574738229a", "asset_type": "factory"}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-041ccef9d8", "line_id": "L-574738229a", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2813,23 +2813,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>333</v>
+        <v>229</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-574738229a", "asset_type": "production_line"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2839,23 +2839,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>325</v>
+        <v>215</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2865,23 +2865,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>311</v>
+        <v>215</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-4-0164", "receivable_term_quarters": 4, "revenue_wan": 134.0}</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2891,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>-48</v>
       </c>
       <c r="E43" t="n">
-        <v>297</v>
+        <v>167</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
         </is>
       </c>
     </row>
@@ -2917,23 +2917,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>-32</v>
       </c>
       <c r="E44" t="n">
-        <v>283</v>
+        <v>135</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-447e1e2775", "line_id": "L-574738229a", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>269</v>
+        <v>121</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v>-15</v>
       </c>
       <c r="E46" t="n">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3047,14 +3047,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="E49" t="n">
-        <v>246</v>
+        <v>92</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3080,11 +3080,11 @@
         <v>-14</v>
       </c>
       <c r="E50" t="n">
-        <v>232</v>
+        <v>78</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3106,11 +3106,11 @@
         <v>-14</v>
       </c>
       <c r="E51" t="n">
-        <v>218</v>
+        <v>64</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3125,14 +3125,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>-14</v>
+        <v>134</v>
       </c>
       <c r="E52" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-1c63be89ff"}</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3158,7 @@
         <v>-15</v>
       </c>
       <c r="E53" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -3558,7 +3558,7 @@
         <v>79</v>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -3611,13 +3611,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F16" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3636,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3661,13 +3661,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3695,7 +3695,7 @@
         <v>79</v>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20">
@@ -3711,16 +3711,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
+        <v>-68</v>
+      </c>
+      <c r="F20" t="n">
         <v>-79</v>
       </c>
-      <c r="F20" t="n">
-        <v>-50</v>
-      </c>
       <c r="G20" t="n">
-        <v>-79</v>
+        <v>-25</v>
       </c>
       <c r="H20" t="n">
-        <v>-65</v>
+        <v>-57</v>
       </c>
     </row>
     <row r="21">
@@ -3761,16 +3761,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
+        <v>-83.2</v>
+      </c>
+      <c r="F22" t="n">
         <v>-94.2</v>
       </c>
-      <c r="F22" t="n">
-        <v>-65.2</v>
-      </c>
       <c r="G22" t="n">
-        <v>-94.2</v>
+        <v>-40.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-80.2</v>
+        <v>-72.2</v>
       </c>
     </row>
     <row r="23">
@@ -3811,16 +3811,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-104.2</v>
+        <v>-83.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-65.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-94.2</v>
+        <v>-40.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-80.2</v>
+        <v>-72.2</v>
       </c>
     </row>
     <row r="25">
@@ -3861,16 +3861,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-104.2</v>
+        <v>-83.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-65.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-94.2</v>
+        <v>-40.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-80.2</v>
+        <v>-72.2</v>
       </c>
     </row>
     <row r="28">
@@ -3960,16 +3960,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="F30" t="n">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="G30" t="n">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="H30" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31">
@@ -3985,13 +3985,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4010,13 +4010,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4035,16 +4035,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -4085,16 +4085,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="F35" t="n">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="G35" t="n">
-        <v>274</v>
+        <v>320</v>
       </c>
       <c r="H35" t="n">
-        <v>209</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36">
@@ -4210,16 +4210,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>484.6</v>
+        <v>505.6</v>
       </c>
       <c r="F40" t="n">
-        <v>419.4</v>
+        <v>411.4</v>
       </c>
       <c r="G40" t="n">
-        <v>325.2</v>
+        <v>371.2</v>
       </c>
       <c r="H40" t="n">
-        <v>245</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41">
@@ -4385,16 +4385,16 @@
         <v>-4.263256414560601e-14</v>
       </c>
       <c r="E47" t="n">
-        <v>-86.20000000000003</v>
+        <v>-86.20000000000009</v>
       </c>
       <c r="F47" t="n">
-        <v>-190.4</v>
+        <v>-169.4000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>-255.6</v>
+        <v>-263.6000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>-349.8</v>
+        <v>-303.8000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -4410,16 +4410,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-104.2</v>
+        <v>-83.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-65.2</v>
+        <v>-94.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-94.2</v>
+        <v>-40.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-80.2</v>
+        <v>-72.2</v>
       </c>
     </row>
     <row r="49">
@@ -4435,16 +4435,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>484.6</v>
+        <v>505.5999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>419.4</v>
+        <v>411.3999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>325.2</v>
+        <v>371.1999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>245</v>
+        <v>298.9999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4460,16 +4460,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>484.6</v>
+        <v>505.5999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>419.4</v>
+        <v>411.3999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>325.2</v>
+        <v>371.1999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>245</v>
+        <v>298.9999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4689,7 +4689,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4987,7 +4987,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5136,7 +5136,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
